--- a/data/trans_orig/IP1001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>99854</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105723</t>
+          <t>105716</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114380</t>
+          <t>113849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>120555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217042</t>
+          <t>218020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225353</t>
+          <t>225568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>247161</t>
+          <t>247083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252564</t>
+          <t>252498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246501</t>
+          <t>247047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252491</t>
+          <t>252542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495519</t>
+          <t>495628</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>504191</t>
+          <t>503813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7015</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117505</t>
+          <t>117651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124924</t>
+          <t>124872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130868</t>
+          <t>130691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138591</t>
+          <t>138424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251485</t>
+          <t>251390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262048</t>
+          <t>261640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177624</t>
+          <t>178049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188142</t>
+          <t>188019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194152</t>
+          <t>193786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202771</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375433</t>
+          <t>375325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388229</t>
+          <t>388413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50416</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>652870</t>
+          <t>652026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>667138</t>
+          <t>666395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>695492</t>
+          <t>695430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>709467</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353305</t>
+          <t>1353277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373109</t>
+          <t>1373047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140193</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145631</t>
+          <t>145594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140042</t>
+          <t>140546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282584</t>
+          <t>282935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289400</t>
+          <t>289456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224853</t>
+          <t>225117</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>232692</t>
+          <t>232917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254554</t>
+          <t>254824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264208</t>
+          <t>263646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>484299</t>
+          <t>483401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495718</t>
+          <t>495446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147959</t>
+          <t>148543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154180</t>
+          <t>154834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149895</t>
+          <t>149662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157304</t>
+          <t>157290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301645</t>
+          <t>301757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310552</t>
+          <t>310774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161910</t>
+          <t>161775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169508</t>
+          <t>169432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165006</t>
+          <t>164565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174343</t>
+          <t>173895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331509</t>
+          <t>330578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342011</t>
+          <t>342402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>686636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698439</t>
+          <t>699072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719808</t>
+          <t>719904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734724</t>
+          <t>735327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1411447</t>
+          <t>1411506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1430881</t>
+          <t>1431067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128602</t>
+          <t>128080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120237</t>
+          <t>120575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250511</t>
+          <t>251084</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255264</t>
+          <t>255258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8078</t>
+          <t>8143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>16128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202439</t>
+          <t>202374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208775</t>
+          <t>208733</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247811</t>
+          <t>247282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>255150</t>
+          <t>255107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452812</t>
+          <t>452450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462706</t>
+          <t>462484</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23665</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173806</t>
+          <t>173904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184018</t>
+          <t>184278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177084</t>
+          <t>177312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185684</t>
+          <t>185574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353806</t>
+          <t>354889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367455</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167940</t>
+          <t>167472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172692</t>
+          <t>172682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162765</t>
+          <t>162600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171168</t>
+          <t>171017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333818</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343130</t>
+          <t>342932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46007</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>680332</t>
+          <t>680566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>693939</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>718119</t>
+          <t>716959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>732128</t>
+          <t>731517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403208</t>
+          <t>1404303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1423061</t>
+          <t>1423415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57852</t>
+          <t>57909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115358</t>
+          <t>115321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151648</t>
+          <t>152056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158126</t>
+          <t>158149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174313</t>
+          <t>174158</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181359</t>
+          <t>181492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330063</t>
+          <t>328708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338588</t>
+          <t>338527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>163035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170843</t>
+          <t>171465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191093</t>
+          <t>189874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208438</t>
+          <t>208444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356220</t>
+          <t>359504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377906</t>
+          <t>377710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263654</t>
+          <t>262768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272888</t>
+          <t>272671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283840</t>
+          <t>284215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>298040</t>
+          <t>297684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550442</t>
+          <t>551728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>568279</t>
+          <t>568183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8708</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56621</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643379</t>
+          <t>643907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>656632</t>
+          <t>656616</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>721801</t>
+          <t>720777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744728</t>
+          <t>743244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1370691</t>
+          <t>1369179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396983</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1001-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1001-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7661</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2145</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6317</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6169</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2940</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7531</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118440</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>113719</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120557</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104026</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>99854</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>105716</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>105721</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118440</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>113849</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120555</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218020</t>
+          <t>216559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225568</t>
+          <t>225294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2587</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6122</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6053</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6709</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>250436</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>246395</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>252489</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>250618</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>247083</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>252498</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>247152</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>252501</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,72%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>250436</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>247047</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>252542</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>752</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495628</t>
+          <t>496313</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503813</t>
+          <t>504071</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5537</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2676</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9897</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9726</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6130</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3091</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10824</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135385</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>130081</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138507</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122011</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>117651</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>124872</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>117822</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>124950</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135385</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130691</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>138424</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>251390</t>
+          <t>251655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261640</t>
+          <t>262079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6887</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11710</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>10266</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6078</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16048</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6184</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16723</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6887</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3744</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12263</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>194339</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202587</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>183831</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>178049</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>188019</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>177374</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>187913</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>199162</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>193786</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202305</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375325</t>
+          <t>375297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>388413</t>
+          <t>388535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13421</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27329</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28995</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29054</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13052</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27270</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50444</t>
+          <t>50899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1057</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>703423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>695371</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>709279</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>987</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>660486</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>652026</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>666395</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>651967</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>666720</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>703423</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>695430</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>709648</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353277</t>
+          <t>1352822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373047</t>
+          <t>1372802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3943</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2586</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6373</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3967</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143215</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140570</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>143695</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>139908</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>145594</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>139745</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>145602</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143215</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140546</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>282935</t>
+          <t>283029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289456</t>
+          <t>289495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3942</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12551</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4237</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9359</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9320</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7291</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4070</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12892</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>260425</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>255165</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>263774</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>230239</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225117</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>232917</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>225156</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>232682</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>260425</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>254824</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>263646</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>483401</t>
+          <t>484225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495446</t>
+          <t>495388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267716</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267716</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267716</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267716</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267716</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3894</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2267</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6291</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3894</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1281</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8909</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154677</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149789</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157301</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152567</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148543</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154834</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148303</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154177</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154677</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149662</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157290</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301757</t>
+          <t>300955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310774</t>
+          <t>310543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7530</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4141</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12626</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4359</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1601</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8942</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7530</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4062</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13392</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170427</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>165331</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173816</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>166978</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161775</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169432</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>162395</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>169736</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>170427</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164565</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173895</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330578</t>
+          <t>330538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342402</t>
+          <t>342472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28897</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20292</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20330</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13431</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>28854</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>24595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>44948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>728745</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>719861</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>735171</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>999</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>693480</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>686636</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>699072</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>686598</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>698696</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>728745</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>719904</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>735327</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1411506</t>
+          <t>1410738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1431067</t>
+          <t>1431091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1183</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3726</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3574</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3589</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>122981</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120438</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131050</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128080</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>129193</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>122981</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>120575</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>395</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251084</t>
+          <t>250494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255258</t>
+          <t>255260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10547</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4302</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1784</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8143</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8593</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,04%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5661</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2954</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10779</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16128</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>252400</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>247514</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>255483</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>206215</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>202374</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>208733</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>201924</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>208720</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,96%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>252400</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>247282</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>255107</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>696</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452450</t>
+          <t>452983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462484</t>
+          <t>462449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2851</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11410</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8771</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4621</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14995</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4748</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15444</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11260</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>182236</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>177162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>185721</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>180128</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>173904</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>184278</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>173455</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>184151</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,36%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182236</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>177312</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>185574</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354889</t>
+          <t>354732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367642</t>
+          <t>367848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2912</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11839</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5829</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5777</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3031</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11448</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>167975</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>162209</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171136</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171217</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167472</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>172682</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167524</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>172689</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>167975</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>162600</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171017</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333438</t>
+          <t>333678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342932</t>
+          <t>343031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27863</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23805</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10036</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23232</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13327</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27885</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>46378</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>725591</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>716981</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>731819</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1038</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>688610</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>680566</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>693855</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>681139</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>694335</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>725591</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716959</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>731517</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1404303</t>
+          <t>1402837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1423415</t>
+          <t>1422810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45709</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60720</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57909</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118231</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115321</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13145</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154200</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>149399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156402</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>156170</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>152056</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158149</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>178904</t>
+          <t>142402</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>174158</t>
+          <t>138628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181492</t>
+          <t>144500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>335074</t>
+          <t>296602</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>328708</t>
+          <t>290807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338527</t>
+          <t>299926</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13038</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4751</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1607</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10037</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22616</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>11675</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>193425</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>187088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>196727</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>168321</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>163035</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171465</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>203075</t>
+          <t>169698</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189874</t>
+          <t>164492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208444</t>
+          <t>172939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>371397</t>
+          <t>363123</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>359504</t>
+          <t>355609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377710</t>
+          <t>368171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,107 +7593,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12908</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7470</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21113</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6215</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2787</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12690</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6503</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3082</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12606</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>19411</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>12425</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>28177</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13371</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7799</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21268</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>19586</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>12757</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>29212</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7706,107 +7706,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>279737</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>271532</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>285175</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>269243</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>262768</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>272671</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>250050</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>243947</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>253471</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>529787</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>521021</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>536773</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>97,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>292112</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>284215</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>297684</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>561354</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>551728</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>568183</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16067</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33293</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21433</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58133</t>
+          <t>50180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677255</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667536</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684762</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>923</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>651245</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>643907</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>656616</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>734812</t>
+          <t>614241</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>720777</t>
+          <t>605258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>743244</t>
+          <t>619571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1386057</t>
+          <t>1291496</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1369179</t>
+          <t>1279482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396457</t>
+          <t>1301282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
